--- a/data/church_directory.xlsx
+++ b/data/church_directory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:J305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6127,2870 +6127,8746 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Baker Assembly of God</t>
+          <t>Council Valley Assembly of God</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>801 Colorado Ave</t>
+          <t>500 E Whiteley Ave</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Council</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>59313</t>
+          <t>83612</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>406-778-3785</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>info@bakerassembly.com</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>bakerassembly.com</t>
-        </is>
-      </c>
+          <t>208-253-6430</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Rod Kilsdonk</t>
+          <t>K Geoffrey Cole</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Belgrade Christian Assembly</t>
+          <t>Crossroads Assembly of God</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>103 E Cascade Ave</t>
+          <t>20444 Hwy 95</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgrade</t>
+          <t>Wilder</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>59714</t>
+          <t>83676</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>406-388-6014</t>
+          <t>208-890-3046</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>spirit.org</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>James R Crossley</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bigfork Chapel</t>
+          <t>First Assembly of Rupert</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>290 Swan Hwy</t>
+          <t>402 H St</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bigfork</t>
+          <t>Rupert</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>59911</t>
+          <t>83350</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>406-837-6087</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>info@bigforkchapel.org</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>bigforkchapel.org</t>
-        </is>
-      </c>
+          <t>208-436-6907</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Chad Peterson</t>
+          <t>Daniel R Hendricks</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Canvas Church – Kalispell</t>
+          <t>Firth Tabernacle Assembly of God</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>255 Summit Ridge Dr</t>
+          <t>235 W Center St</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kalispell</t>
+          <t>Firth</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>83236</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>406-752-6426</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>office@canvas.church</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>canvas.church</t>
-        </is>
-      </c>
+          <t>208-346-6911</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Kevin Greer</t>
+          <t>Dan E Mielke</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Central Assembly of God – Great Falls</t>
+          <t>Fort Hall Assembly of God</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2001 Central</t>
+          <t>1381 Cave</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Great Falls</t>
+          <t>Fort Hall</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>59401</t>
+          <t>83203</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>406-453-5524</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>info@centralgf.com</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>centralgf.com</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Alan Warneke</t>
-        </is>
-      </c>
+          <t>208-237-1771</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Christian Life Center – Missoula</t>
+          <t>Hagerman Christian Center</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3801 S Russell St</t>
+          <t>2750 S 900 E</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Missoula</t>
+          <t>Hagerman</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>83332</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>406-542-0353</t>
+          <t>208-837-6140</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>info@missoulachurch.com</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>missoulachurch.com</t>
-        </is>
-      </c>
+          <t>pastortellez@gmail.com</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Heath McCoy</t>
+          <t>Daniel Isaac Tellez</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Connect Church</t>
+          <t>Highway Worship Center A/G</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>549 Pronghorn Trail</t>
+          <t>100 S Whitley Dr</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bozeman</t>
+          <t>Fruitland</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
+          <t>83619</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>208-452-3437</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>info@connectchurchonline.com</t>
+          <t>hiwayag@fmtc.com</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>connectchurch.app</t>
+          <t>fruitlandchurch.com</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Russ Michaels</t>
+          <t>Danny L Formhals</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Deer Lodge Assembly of God</t>
+          <t>Idaho City Christian Center</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>601 5th St</t>
+          <t>3853 Hwy 21</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Deer Lodge</t>
+          <t>Idaho City</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>59722</t>
+          <t>83631</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>406-846-1056</t>
+          <t>208-392-4218</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>pastordaviddlag@gmail.com</t>
+          <t>IdahoCityChristianCenter@gmail.com</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>DeerLodgeAssembly.org</t>
+          <t>idahocitychristiancenter.com</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>David Baker</t>
+          <t>Jason W Kindelberger</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dillon Assembly</t>
+          <t>Life Church of the Magic Valley</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>104 S California</t>
+          <t>425 E Nez Perce</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dillon</t>
+          <t>Jerome</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>59725</t>
+          <t>83338</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>406-683-4689</t>
+          <t>208-324-5876</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>dillonassem@gmail.com</t>
+          <t>rbrt.groves@lifechurchmv.com</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>dillonassembly.com</t>
+          <t>lifechurchmv.com</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>James Matthews</t>
+          <t>Kevin A Ashley</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Echo Church</t>
+          <t>Lighthouse Assembly of God – Blackfoot</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2210 Dodge Ave</t>
+          <t>288 W Pacific</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Blackfoot</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>59601</t>
+          <t>83221</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>406-442-6851</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>info@helenafirstassembly.com</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>helenafirst.com</t>
-        </is>
-      </c>
+          <t>208-557-8811</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Paul Feuerstein</t>
+          <t>David A Trevizo</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Family Church – Laurel</t>
+          <t>Magic Valley Family Church</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1002 3rd Avenue</t>
+          <t>319 2nd St E</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Laurel</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>59044</t>
+          <t>83334</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>406-628-4200</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>info@familychurchlaurel.com</t>
-        </is>
-      </c>
+          <t>208-423-5224</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>familychurchlaurel.com</t>
+          <t>hansenassemblyofgod.org</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>John &amp; Catherine Farnes</t>
+          <t>Bruce M Murray</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Hamilton Assembly</t>
+          <t>Magic Valley Worship Center</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>601 W Main</t>
+          <t>302 3rd Ave E</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Twin Falls</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>83301</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>406-363-2510</t>
+          <t>208-536-0158</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>hamiltonag.org</t>
-        </is>
-      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>John Weaver</t>
+          <t>Jim B Pollard</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Havre Assembly of God</t>
+          <t>Marsing Assembly of God</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>905 9th St West</t>
+          <t>139 Kerry St</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Havre</t>
+          <t>Marsing</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>83639</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>406-265-5803</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>havreag@mtintouch.net</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>havreassembly.org</t>
-        </is>
-      </c>
+          <t>208-965-1650</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Edroy Curtis II</t>
+          <t>Sergio Aristizabal</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Journey Church – Butte</t>
+          <t>Melba Valley Worship Center</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2055 Florence Ave</t>
+          <t>1263 Hwy 45</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Butte</t>
+          <t>Melba</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>83641</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>406-723-5543</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>info@buttechurch.com</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>buttechurch.com</t>
-        </is>
-      </c>
+          <t>208-495-1240</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Randy Lindgren</t>
+          <t>Michael J Gregg</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Libby Church</t>
+          <t>Mountain View Christian Center – Burley</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>105 Collins Ave</t>
+          <t>317 Mountain View Ln</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Libby</t>
+          <t>Burley</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>59923</t>
+          <t>83318</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>406-293-8331</t>
+          <t>208-678-5460</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>info@libbychurch.com</t>
+          <t>burleyccag@burleyccag.org</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>libbychurch.com</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>MvccChurch.org</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Joshua E Merchant</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>The Lighthouse – Miles City</t>
+          <t>New Heart Assembly of God</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3300 Horizon Parkway</t>
+          <t>246 W 1st St</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miles City</t>
+          <t>Glenns Ferry</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>83623</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>406-234-5559</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>info@milecitychurch.com</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>milescitychurch.com</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>208-943-1336</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Katie A Shenk</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Livingston Christian Center</t>
+          <t>New Hope Assembly of God – Challis</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1400 Mount Baldy Dr</t>
+          <t>1030 S Custer St</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Challis</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>83226</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>406-222-3144</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>office@livingstonchristiancenter.com</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Livingstonchristiancenter.com</t>
-        </is>
-      </c>
+          <t>208-879-4620</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>David Brakke Sr</t>
+          <t>William Matthews</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>New Life Assembly – Lewistown</t>
+          <t>New Life Assembly – Rupert</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>515 7th Ave N</t>
+          <t>254 S Hwy 24</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lewistown</t>
+          <t>Rupert</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>59457</t>
+          <t>83350</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>406-535-7095</t>
+          <t>208-434-2004</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>info@lewistownnewlife.org</t>
+          <t>nlaheyburn@gmail.com</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>lewistownnewlife.org</t>
+          <t>newlifeidaho.com</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Ken Loss</t>
+          <t>Daniel W Renz</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>New Life Christian Center – Polson</t>
+          <t>Open Arms</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1414 Second St W</t>
+          <t>11 S Hooper Ave</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Polson</t>
+          <t>Soda Springs</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>59860</t>
+          <t>83276</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>406-883-2447</t>
+          <t>208-317-2933</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>office@newlifepolson.com</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>newlifepolson.com</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Chris Sopke</t>
-        </is>
-      </c>
+          <t>PCAssembly@gmail.com</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Northwest Family Fellowship</t>
+          <t>Powerhouse Christian Fellowship</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>300 23rd Ave NE</t>
+          <t>2905 Sunbeam</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Great Falls</t>
+          <t>American Falls</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>59404</t>
+          <t>83211</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>406-727-6933</t>
+          <t>208-226-5998</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>office@nwff.org</t>
+          <t>secretary@phcf.org</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>nwff.org</t>
+          <t>phcf.org</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mark Jones</t>
+          <t>Tyler S Hayes</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Parkhill Church</t>
+          <t>Revelation Church</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1707 Parkhill Dr</t>
+          <t>908 Specht Ave</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Billings</t>
+          <t>Caldwell</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>83605</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>406-259-7294</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>info@parkhillchurch.net</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>parkhillchurch.net</t>
-        </is>
-      </c>
+          <t>208-870-8979</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Jon Warneke</t>
+          <t>Mark P Bridgewater</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Summit Church – Bozeman</t>
+          <t>Riggins Assembly of God</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>921 W Mendenhall St</t>
+          <t>1015 S Main</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bozeman</t>
+          <t>Riggins</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>59715</t>
+          <t>83549</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>406-587-9283</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>info@bozemanchristiancenter.org</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>summitchurchmt.com</t>
-        </is>
-      </c>
+          <t>208-459-4065</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Lance Steeves</t>
+          <t>James R Dunn</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Whitefish Assembly</t>
+          <t>River City Church of Boise</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>150 Lamb Ln</t>
+          <t>7540 Northview St</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Whitefish</t>
+          <t>Boise</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>83704</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>406-862-4039</t>
+          <t>208-375-1328</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>aog@whitefishaog.com</t>
+          <t>info@nfwcboise.org</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>whitefishaog.com</t>
+          <t>nfwcboise.com</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shawn Madsen</t>
+          <t>E Wayne Crownover</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Wolf Point Assembly of God</t>
+          <t>River of Life Christian Center – Payette</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>616 4th Ave N</t>
+          <t>800 17th Ave N</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wolf Point</t>
+          <t>Payette</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>83661</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>406-653-1732</t>
+          <t>208-642-3601</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>wpaog@yahoo.com</t>
+          <t>info@riverlcc.org</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>wolfpointaog.org</t>
+          <t>riveroflifecc.net</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Richard Coker</t>
+          <t>Wayne W White</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Abundant Life Assembly of God – Enterprise</t>
+          <t>River of Life Church – Pocatello</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>207 E Main St</t>
+          <t>1211 S 5th Ave</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pocatello</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>83201</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>541-426-3752</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+          <t>208-232-3946</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>info@riverchurch.us</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>riveroflifeidaho.com</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>James E Hambelton</t>
+          <t>Matthew J Moretti</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Bethel Church – Pendleton</t>
+          <t>Sunnyridge Assembly of God</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1109 Airport Rd</t>
+          <t>2121 Sunnyridge Rd</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pendleton</t>
+          <t>Nampa</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>97801</t>
+          <t>83686</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>541-276-7559</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Bethelchurchpendleton@gmail.com</t>
-        </is>
-      </c>
+          <t>208-466-3668</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Timothy J Van Cleave</t>
+          <t>Robert D Wright</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Faith Christian Center – Bend</t>
+          <t>The Rock – Hailey</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1049 NE 11th St</t>
+          <t>511 N Main St</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bend</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>97701</t>
+          <t>83333</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>541-382-8274</t>
+          <t>208-788-5470</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>kays@bendfcc.com</t>
+          <t>Pastor@woodriverag.com</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>bendfaith.com</t>
+          <t>therockchurchwrv.org</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mark A Gering</t>
+          <t>Konrad F Ziesing</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>First Assembly of God – Pendleton</t>
+          <t>The Rock – Mountain Home</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1911 SE Court St</t>
+          <t>315 S 4th E</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pendleton</t>
+          <t>Mountain Home</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>97801</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>83647</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>208-587-3632</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>contactus@pendletonfirst.com</t>
+          <t>churchoffice@lifeattherock.com</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>pendletonfirst.com</t>
+          <t>lifeattherock.com</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Joshua P Brunette</t>
+          <t>Andrew S Bailey</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Hermiston Christian Center</t>
+          <t>Valley Christian Center – Horseshoe Bend</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1825 W Highland</t>
+          <t>109 S Riverside</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hermiston</t>
+          <t>Horseshoe Bend</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>97838</t>
+          <t>83629</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>541-567-3480</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>hcc4u@machmedia.net</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>hcc4u.org</t>
-        </is>
-      </c>
+          <t>208-793-2448</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Dale W Larson</t>
+          <t>H Martin Broom</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Life In Christ Center</t>
+          <t>Westside Assembly of God</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3095 Cherry Heights</t>
+          <t>4025 Hwy 30 W</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>The Dalles</t>
+          <t>New Plymouth</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>83655</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>541-296-1136</t>
+          <t>208-953-7350</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>hello@lifeinchrist.church</t>
+          <t>npassembly@aol.com</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>lifeinchrist.church</t>
+          <t>npaog.com</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Allen D Refsland</t>
+          <t>Jonathan J Baker</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>ID – Southern</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lighthouse Worship Center – Ontario</t>
+          <t>Baker Assembly of God</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>96 SW 2nd St</t>
+          <t>801 Colorado Ave</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>97914</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>59313</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>406-778-3785</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>infolwwondroo@gmail.com</t>
+          <t>info@bakerassembly.com</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>lwcontariochurch.com</t>
+          <t>bakerassembly.com</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Joshua D Wolfe</t>
+          <t>Rod Kilsdonk</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Mountain Life Church</t>
+          <t>Belgrade Christian Assembly</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>10700 S Walton Rd</t>
+          <t>103 E Cascade Ave</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>La Grande</t>
+          <t>Belgrade</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>97850</t>
+          <t>59714</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>541-805-0073</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>admin@nlcag.org</t>
-        </is>
-      </c>
+          <t>406-388-6014</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>mtnlifechurch.com</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Jerad M Upwall</t>
-        </is>
-      </c>
+          <t>spirit.org</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Outback Assembly of God</t>
+          <t>Bigfork Chapel</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1014 Center</t>
+          <t>290 Swan Hwy</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lakeview</t>
+          <t>Bigfork</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>97630</t>
+          <t>59911</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>541-947-2520</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr"/>
+          <t>406-837-6087</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>info@bigforkchapel.org</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>outback.church</t>
+          <t>bigforkchapel.org</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Gerald Elrod</t>
+          <t>Chad Peterson</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Redmond Assembly of God</t>
+          <t>Canvas Church – Kalispell</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1865 W Antler Ave</t>
+          <t>255 Summit Ridge Dr</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Kalispell</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>97756</t>
-        </is>
-      </c>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>541-548-4555</t>
+          <t>406-752-6426</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>revdet@aol.com</t>
+          <t>office@canvas.church</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>redmondag.com</t>
+          <t>canvas.church</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>G Duane Pippitt</t>
+          <t>Kevin Greer</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Refuge</t>
+          <t>Central Assembly of God – Great Falls</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2610 Shosta Wy</t>
+          <t>2001 Central</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Klamath Falls</t>
+          <t>Great Falls</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>541-882-1668</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
+          <t>406-453-5524</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>info@centralgf.com</t>
+        </is>
+      </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>refugecity.church</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>centralgf.com</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Alan Warneke</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>River of Life Assembly – Hood River</t>
+          <t>Christian Life Center – Missoula</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>979 Tucker Rd</t>
+          <t>3801 S Russell St</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Missoula</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>97031</t>
+          <t>59801</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>541-386-3656</t>
+          <t>406-542-0353</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>riveroflifeassembly@gmail.com</t>
+          <t>info@missoulachurch.com</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>rolahr.org</t>
+          <t>missoulachurch.com</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Terrell K Abbott</t>
+          <t>Heath McCoy</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Thrive Church</t>
+          <t>Connect Church</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>235 S Laguna St</t>
+          <t>549 Pronghorn Trail</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Klamath Falls</t>
+          <t>Bozeman</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>541-567-5831</t>
-        </is>
-      </c>
+          <t>59719</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>klamathag@charternet.com</t>
+          <t>info@connectchurchonline.com</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>thrivechurchkfalls.org</t>
+          <t>connectchurch.app</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Kevin L Drake</t>
+          <t>Russ Michaels</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Valley Worship Center</t>
+          <t>Deer Lodge Assembly of God</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5780 OR-35</t>
+          <t>601 5th St</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mt Hood</t>
+          <t>Deer Lodge</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>59722</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>541-352-7269</t>
+          <t>406-846-1056</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>valleyworshipcenter.pastor@gmail.com</t>
+          <t>pastordaviddlag@gmail.com</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>valleyworshipcenter.org</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>DeerLodgeAssembly.org</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>David Baker</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Zeal Church</t>
+          <t>Dillon Assembly</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>730 E Hurlburt Ave</t>
+          <t>104 S California</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hermiston</t>
+          <t>Dillon</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>97838</t>
+          <t>59725</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>541-567-5831</t>
+          <t>406-683-4689</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>hello@hermistonassembly.com</t>
+          <t>dillonassem@gmail.com</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>zeal.church</t>
+          <t>dillonassembly.com</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Terry J Haight</t>
+          <t>James Matthews</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Abundant Life Fellowship – Evanston</t>
+          <t>Echo Church</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2190 Wasatch Rd</t>
+          <t>2210 Dodge Ave</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Evanston</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>82930</t>
+          <t>59601</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>307-789-5868</t>
+          <t>406-442-6851</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>stillcreektimf@gmail.com</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>info@helenafirstassembly.com</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>helenafirst.com</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tim Floyd</t>
+          <t>Paul Feuerstein</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Cody Assembly of God</t>
+          <t>Family Church – Laurel</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1532 Bleistein Ave</t>
+          <t>1002 3rd Avenue</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Laurel</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>82414</t>
+          <t>59044</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>307-527-7339</t>
+          <t>406-628-4200</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>codyassembly@yahoo.com</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
+          <t>info@familychurchlaurel.com</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>familychurchlaurel.com</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Cheri Cortez</t>
+          <t>John &amp; Catherine Farnes</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Destiny Church</t>
+          <t>Hamilton Assembly</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>711 Warren</t>
+          <t>601 W Main</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cheyenne</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>82003</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>307-634-4657</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>destinychurchrick@yahoo.com</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
+          <t>406-363-2510</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>hamiltonag.org</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Rick McGraw</t>
+          <t>John Weaver</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Douglas Assembly of God</t>
+          <t>Havre Assembly of God</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>501 S 4th St</t>
+          <t>905 9th St West</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Havre</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>82633</t>
+          <t>59501</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>307-358-3619</t>
+          <t>406-265-5803</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>brossignol85@gmail.com</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
+          <t>havreag@mtintouch.net</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>havreassembly.org</t>
+        </is>
+      </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Brian Rossignol</t>
+          <t>Edroy Curtis II</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>First Assembly of God – Gillette</t>
+          <t>Journey Church – Butte</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>601 Carey</t>
+          <t>2055 Florence Ave</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Gillette</t>
+          <t>Butte</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>82716</t>
+          <t>59701</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>307-682-3308</t>
+          <t>406-723-5543</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>dmholden@juno.com</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
+          <t>info@buttechurch.com</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>buttechurch.com</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Dan Holden</t>
+          <t>Randy Lindgren</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>First Assembly of God – Riverton</t>
+          <t>Libby Church</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>701 E Adams</t>
+          <t>105 Collins Ave</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Riverton</t>
+          <t>Libby</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>82501</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>307-856-3637</t>
+          <t>406-293-8331</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>mmbrumback@gmail.com</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Michael Brumback</t>
-        </is>
-      </c>
+          <t>info@libbychurch.com</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>libbychurch.com</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>First Assembly of God – Rock Springs</t>
+          <t>The Lighthouse – Miles City</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2191 Century Blvd</t>
+          <t>3300 Horizon Parkway</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Rock Springs</t>
+          <t>Miles City</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>82902</t>
+          <t>59301</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>307-362-8665</t>
+          <t>406-234-5559</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>tnheidt@yahoo.com</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Nicole Heidt</t>
-        </is>
-      </c>
+          <t>info@milecitychurch.com</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>milescitychurch.com</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>First Assembly of God – Sheridan</t>
+          <t>Livingston Christian Center</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1045 Lewis St</t>
+          <t>1400 Mount Baldy Dr</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sheridan</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>82801</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>307-674-6372</t>
+          <t>406-222-3144</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>firstassemblysheridan@gmail.com</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+          <t>office@livingstonchristiancenter.com</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Livingstonchristiancenter.com</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>David Brakke Sr</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Glad Tidings Assembly of God</t>
+          <t>New Life Assembly – Lewistown</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>777 E 7th St</t>
+          <t>515 7th Ave N</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Powell</t>
+          <t>Lewistown</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>82435</t>
+          <t>59457</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>307-754-2333</t>
+          <t>406-535-7095</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>pastormikewalsh@yahoo.com</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>info@lewistownnewlife.org</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>lewistownnewlife.org</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Michael Walsh</t>
+          <t>Ken Loss</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Green River Assembly of God</t>
+          <t>New Life Christian Center – Polson</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1380 Hitching Post Dr</t>
+          <t>1414 Second St W</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Green River</t>
+          <t>Polson</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>82935</t>
+          <t>59860</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>307-875-6232</t>
+          <t>406-883-2447</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>agfirstgr@gmail.com</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>office@newlifepolson.com</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>newlifepolson.com</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Shawn Johnston</t>
+          <t>Chris Sopke</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Impact Ministries</t>
+          <t>Northwest Family Fellowship</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>956 Maple St</t>
+          <t>300 23rd Ave NE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wheatland</t>
+          <t>Great Falls</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>59404</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>307-331-7544</t>
+          <t>406-727-6933</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>jharoldson.impact@hotmail.com</t>
+          <t>office@nwff.org</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>impactwy.org</t>
+          <t>nwff.org</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Jeremy Haroldson</t>
+          <t>Mark Jones</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Living Waters Assembly of God</t>
+          <t>Parkhill Church</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>318 N 8th St</t>
+          <t>1707 Parkhill Dr</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Thermopolis</t>
+          <t>Billings</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>82443</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>307-864-3677</t>
+          <t>406-259-7294</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>lwagthermopolis@gmail.com</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr"/>
+          <t>info@parkhillchurch.net</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>parkhillchurch.net</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Michael Muench</t>
+          <t>Jon Warneke</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>New Life Assembly of God – Buffalo</t>
+          <t>Summit Church – Bozeman</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6 Barstad Way</t>
+          <t>921 W Mendenhall St</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Bozeman</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>82834</t>
+          <t>59715</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>307-684-5755</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
+          <t>406-587-9283</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>info@bozemanchristiancenter.org</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>summitchurchmt.com</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Josh &amp; Whitney Davies</t>
+          <t>Lance Steeves</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>New Life Assembly of God – Laramie</t>
+          <t>Whitefish Assembly</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3905 E Grey Cable</t>
+          <t>150 Lamb Ln</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Laramie</t>
+          <t>Whitefish</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>82072</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>307-460-3351</t>
+          <t>406-862-4039</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>info@newlifelaramie.org</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
+          <t>aog@whitefishaog.com</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>whitefishaog.com</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Matt Baumgartner</t>
+          <t>Shawn Madsen</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Radius Church</t>
+          <t>Wolf Point Assembly of God</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4301 Casper Mountain Rd</t>
+          <t>616 4th Ave N</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Casper</t>
+          <t>Wolf Point</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>82601</t>
+          <t>59201</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>307-265-9121</t>
+          <t>406-653-1732</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>contact@radiuschurch.life</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
+          <t>wpaog@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>wolfpointaog.org</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Craig Mellendorf</t>
+          <t>Richard Coker</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Summit Church – Big Piney</t>
+          <t>Billings Praise Center</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3 Winkelman Ave</t>
+          <t>516 S 37th St</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Marbleton</t>
+          <t>Billings</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>83113</t>
-        </is>
-      </c>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>307-875-5212</t>
+          <t>406-245-7609</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>summitchurchwy@gmail.com</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
+          <t>mtdreamcenter@outlook.com</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>montanadreamcenter.com</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sunrise Assembly of God – Sheridan</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>570 Marion St</t>
-        </is>
-      </c>
+          <t>Boulder Assembly of God</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Sheridan</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>82801</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>307-674-8424</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>nnjjjackson@gmail.com</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
+          <t>406-225-384</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>boulderassemblyofgod.com</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>John Jackson</t>
+          <t>Duane Weinmeister</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Trinity Assembly of God</t>
+          <t>Bridge Assembly</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>604 9th St</t>
+          <t>725 Granite Ave</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Rawlins</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>82301</t>
+          <t>59601</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>307-324-2635</t>
+          <t>406-442-8523</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>kk_sherman@hotmail.com</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>hello@bridgehelena.com</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>bridgehelena.com</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Kirk Sherman</t>
+          <t>Jason Metz</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
+          <t>Broadus Assembly of God</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>16 US 212 E</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Broadus</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>59317</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>406-436-2114</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>BroadusAG@agchurches.org</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>John Wilson</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Busby Assembly of God</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Busby</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>59016</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>406-592-3592</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Kent Burnett</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Canyon Life Church</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>19 Central</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>59421</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>406-468-5064</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>canyonlifechurch.com</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Mark Nelsen</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Chapel of Hope</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2425 Hwy 87 E</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Billings</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>59101</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>406-256-2328</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>info@billingshope.com</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>billingshope.com</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Rick Grieve</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Chester Assembly of God</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Chester</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>59522</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>406-759-5692</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>connect@chesterassembly.com</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>chesterassembly.com</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Chad Smith</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Chief Cornerstone</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>9398 Mountain Crow Rd</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Crow Agency</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>59022</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>406-679-1880</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>vienne_stewart@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Jay Simpson</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Chinook Assembly</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>113 4th W</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Chinook</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>59523</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>406-357-2425</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>transformchinook.com</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Christian Center – Three Forks</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>315 1st W</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Three Forks</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>59752</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>406-285-4305</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Church On The Move</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>301 Central</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Plains</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>59859</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>406-826-3800</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>cotmplains@gmail.com</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Chuck Standeford</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Cornerstone Faith Center – St Ignatius</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>St Ignatius</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>59865</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>406-745-3455</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>saintigag@gmail.com</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>cornerstonefaithcenter.com</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Eric Reed</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ennis Assembly of God</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ennis</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>59729</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>406-682-4197</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>ennisassembly@gmail.com</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Greg Ledgerwood</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Faith Assembly of God – Circle</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>59215</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>406-485-3347</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>faithassemblymt.com</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Owen Childers</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Faith Chapel – Harlowton</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>601 NW Anchard</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Harlowton</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>406-632-4866</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>faithinharlo.com</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Fairfield Assembly of God</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>59436</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>406-467-2713</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Mike Manuel</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Forsyth Assembly of God</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>59327</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>406-346-263</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>office@forsythassemblyofgod.com</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Dan Sand</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Four Winds Assembly of God</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Browning</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>59417</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>406-338-3077</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>fourwindsaog.com</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Joel Toppen</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Gateway Christian Fellowship – Anaconda</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>300 E 4th</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Anaconda</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>59711</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>406-563-3534</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>info@gatewaymt.com</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>gatewaymt.com</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Generations Church – Billings</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2345 Hawthorne Ln</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Billings</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>59105</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>701-989-1945</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Josiah Bruzelius</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Glasgow Assembly of God</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>59230</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>406-228-2694</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>rocksolidyouth@hotmail.com</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>glasgowag.org</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Tom Fauth</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Gospel Mountain</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Thompson Falls</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>59873</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>406-827-4611</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>kristidenson@jesusanswers.com</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>gospelmountainag.org</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Charles Denson</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Harlem Assembly of God</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Harlem</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>59526</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>406-353-2303</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Melissa and Jackson</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Harvest Assembly – Saco</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>109 Nelson St</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Saco</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>59261</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>406-527-3414</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Charles Pople</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Hungry Horse Chapel</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Hungry Horse</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>59919</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>406-387-5807</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>info@hungryhorsechapel.com</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>hungryhorsechapel.com</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Brent Schmidt</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Jordan Assembly of God</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>59337</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>406-557-6140</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>gawwolff@gmail.com</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Greg Wolff</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Journey Church – Columbia Falls</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5091 US 2</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Columbia Falls</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>59912</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>406-730-7282</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>journeychurchcf@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>journeychurchcf.com</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Dave and Erin Vainio</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Life's Journey Christian Fellowship</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>5064 Pinebutte</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Colstrip</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>59323</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>406-740-2225</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>lifesjourneytreasurer@gmail.com</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>lifesjourneymt.com</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Casey Kluver</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Light of the Valley</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>103 N Kootenai Creek Rd</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Stevensville</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>59870</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>406-777-5859</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>office@lightofthevalleyag.com</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>lightofthevalleyag.com</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Brad Rhodda</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Limitless – Sidney</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>414 E Main</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Sidney</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>59270</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>406-433-2550</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>sidneyag@midrivers.com</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sidneyag.com</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Dustin Morgan</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Living the Word – Choteau</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Choteau</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>59422</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>406-466-2303</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>office@newlifewebsite.com</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>livingthewordchoteau.com</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Dale Janzen</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Living Water – Box Elder</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4751 Laredo Rd</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Box Elder</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>59521</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>406-395-5983</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Michael and Kimberly Vohs</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Lodgepole Assembly of God</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HC 63 Box 5248</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Dodson</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>59524</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>406-673-3724</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Doug Jessen</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Malta Assembly of God</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>424 S 3rd</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>406-654-2396</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>maltaag@mtintouch.net</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Tonya Blessing</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Mountain Crow Worship Center</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Pryor</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>59066</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>406-248-7295</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>mountaincrowchurch@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Jay Simpson</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>New Life Glendive</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>921 S Taylor</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Glendive</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>59330</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>406-377-5161</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>gldvassem@midrivers.com</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>newlifeglendive.org</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Kevin Peterson</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>New Life Community Church – Shelby</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>111 Galatin Street</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Shelby</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>59474</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>406-424-8079</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>pemunson@gmail.com</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>newlifeshelby.com</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Eric Munson</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Plentywood Assembly of God</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>426 W First Ave</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Plentywood</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>59254</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>406-765-2991</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>bgsmithson@hotmail.com</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Brandon Smithson</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Poplar Assembly of God</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Poplar</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>59255</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>406-448-2250</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>jay_cummins@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Jay Cummins</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Rock Creek Church</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>417 N Broadway</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Red Lodge</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>59068</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>406-425-3350</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Bob Vande Sandt</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Scobey Assembly of God</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Scobey</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>59263</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>406-487-2603</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>info@scobeyassembly.com</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>South Side Dinner Church</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>24 South 29th</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Billings</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>59101</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>406-286-5315</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>info@mydinnerchurch.org</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>mydinnerchurch.org</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>David &amp; Hailey Brakke</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Spirit of God Ministries</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>511 1st Ave SE</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Ronan</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>59864</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>406-676-8460</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>mtaog@mtaog.org</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Dean Buffalo</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Superior Assembly of God</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>502 2nd E</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Superior</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>59872</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>406-822-5683</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>superiorassemblyofgod@proton.me</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>superiorassembly.org</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Tim &amp; Melanie Fox</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Troy Assembly of God</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>59935</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>406-295-4758</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>tmeroney55@msn.com</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>troyag.org</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Valley Assembly – Sheridan MT</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Sheridan</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>59749</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>406-842-5845</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>valleyassemblysheridan@gmail.com</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>valleyassemblysheridan.com</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Terry Sgrignoli</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Westby Assembly of God</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>613 Sunnyside Ave</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Plentywood</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>59254</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>406-765-1115</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>John Marmon</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Whitehall Assembly</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>61 St St E</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Whitehall</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>59759</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>406-287-3095</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Abundant Life Assembly of God – Enterprise</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>207 E Main St</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>97828</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>541-426-3752</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>James E Hambelton</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Bethel Church – Pendleton</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1109 Airport Rd</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Pendleton</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>97801</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>541-276-7559</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Bethelchurchpendleton@gmail.com</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Timothy J Van Cleave</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Faith Christian Center – Bend</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1049 NE 11th St</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Bend</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>97701</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>541-382-8274</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>kays@bendfcc.com</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>bendfaith.com</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Mark A Gering</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Pendleton</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1911 SE Court St</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Pendleton</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>97801</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>contactus@pendletonfirst.com</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>pendletonfirst.com</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Joshua P Brunette</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Hermiston Christian Center</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1825 W Highland</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Hermiston</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>97838</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>541-567-3480</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>hcc4u@machmedia.net</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>hcc4u.org</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Dale W Larson</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Life In Christ Center</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3095 Cherry Heights</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>The Dalles</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>541-296-1136</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>hello@lifeinchrist.church</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>lifeinchrist.church</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Allen D Refsland</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Lighthouse Worship Center – Ontario</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>96 SW 2nd St</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>97914</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>infolwwondroo@gmail.com</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>lwcontariochurch.com</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Joshua D Wolfe</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Mountain Life Church</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>10700 S Walton Rd</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>La Grande</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>97850</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>541-805-0073</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>admin@nlcag.org</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>mtnlifechurch.com</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Jerad M Upwall</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Outback Assembly of God</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1014 Center</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Lakeview</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>97630</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>541-947-2520</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>outback.church</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Gerald Elrod</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Redmond Assembly of God</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1865 W Antler Ave</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Redmond</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>97756</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>541-548-4555</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>revdet@aol.com</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>redmondag.com</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>G Duane Pippitt</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Refuge</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2610 Shosta Wy</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Klamath Falls</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>541-882-1668</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>refugecity.church</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>River of Life Assembly – Hood River</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>979 Tucker Rd</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>97031</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>541-386-3656</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>riveroflifeassembly@gmail.com</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>rolahr.org</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Terrell K Abbott</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Thrive Church</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>235 S Laguna St</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Klamath Falls</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>97601</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>541-567-5831</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>klamathag@charternet.com</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>thrivechurchkfalls.org</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Kevin L Drake</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Valley Worship Center</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>5780 OR-35</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Mt Hood</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>541-352-7269</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>valleyworshipcenter.pastor@gmail.com</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>valleyworshipcenter.org</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Zeal Church</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>730 E Hurlburt Ave</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Hermiston</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>97838</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>541-567-5831</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>hello@hermistonassembly.com</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>zeal.church</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Terry J Haight</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Butte Falls Assembly of God</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>509 Oak Ave</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Butte Falls</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>97522</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>541-865-3227</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Steven W Harvey</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Chiloquin Christian Center</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>301 Chiloquin Blvd</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Chiloquin</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>541-783-2344</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Mililani Bair</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Christian Center Assembly of God – Huntington</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>595 E Monroe</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Huntington</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>97907</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>541-869-2920</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Christian Life Center – Elgin</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1391 Alder</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Elgin</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>elginchristianlifecenter.com</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Eli L Smith</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Christian Life Center – Heppner</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>535 W Morgan St</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Heppner</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>97836</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>425-218-3711</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Crossroad Community – Stanfield</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>350 NW Sherman</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Stanfield</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>97875</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>541-449-3434</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Family Worship Center – Irrigon</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>330 NE Eighth St</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Irrigon</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>97844</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>541-922-3054</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>irrigonfwc@gmail.com</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>irrigonfwc.org</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Daren C Strong</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Oakridge</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>47949 Hwy 58</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Oakridge</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>97463</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Oakridgeassemblyofgod@gmail.com</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>oakridgeag.org</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Edwin S Novak</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Prineville</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>835 S Main St</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Prineville</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>churchoffice@prinevilleag.com</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>prinevilleag.com</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Aaron Mapes</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Harvest Church A/G – Baker City</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>3720 Birch St</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Baker City</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>541-523-4233</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Bradley W Phillips</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Hope Church – Sweet Home</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>890 Mountain View</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Sweet Home</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>97386</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>541-967-4673</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>T Mark Opperman</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>La Pine Christian Center</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>52565 Day</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>La Pine</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>97739</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>541-536-1593</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>lpccag@qwestoffice.net</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>lapinechristian.org</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Norman R Soyster</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Living Hope Christian Center – Madras</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>25 NE A</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Madras</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>97741</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>541-475-2405</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>office@livinghopecc.com</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>livinghopecc.com</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Brigham Brown</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Living Water Family Fellowship – Blue River</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>52353 McKenzie Hwy</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Blue River</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>97413</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>541-582-1078</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>lwff1@earthlink.net</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>BlueRiver.Church</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Douglas Fairrington</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Mission Assembly of God – Pendleton</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Short Mile Rd</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Pendleton</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>97801</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>541-966-9520</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Dwayne D Winslow</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>New Hope Chapel A/G – Vale</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>477 Oak St</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Vale</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>97918</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>faith_hope_love_worship_center@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>valefaithhopelove.com</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Curtis W Holt</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Pilot Rock Assembly of God</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>123 Beach St</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Pilot Rock</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>97868</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Michael Nelson</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Praise Assembly – Mitchell</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>300 Hwy 26</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>541-269-1727</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Pat and Jalet Farrell</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Prairie City Assembly of God</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>330 SW Front St</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Prairie City</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>97869</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>541-820-3682</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Nathan L Teague</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>RefugeLiving Springs – Bonanza</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>31897 Mission</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Bonanza</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>97623</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>refugecity.church</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>River of Life Assembly – Bingen</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>114 W Jefferson St</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Bingen</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>98605</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>509-386-3656</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Terrell K Abbott</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Shiloh Ranch Cowboy Church</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>15696 SW Bussett</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Powell Butte</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>97753</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>541-410-2444</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Joe G Pearson</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Spray Assembly of God</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>500 Willow St</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Spray</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>97874</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>541-468-2384</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Terrebonne Assembly of God</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>379 NW Smith Rock</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Terrebonne</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>97760</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>541-504-5212</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>terrebonneag.org</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Shannon L Bren</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Umatilla Assembly of God</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>710 L St</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>97882</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>541-922-3462</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Ronald W Honey</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Valley Christian Center – Milton-Freewater</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>800 N Main St</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Milton-Freewater</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>541-938-7161</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>valleycc@oregontrail.net</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>vccag.com</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Shane K Nelson</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Wallowa Assembly of God</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>702 W Hwy 82</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Wallowa</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>97885</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>wallowast@gmail.com</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>wallowaassemblyofgod.com</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Timothy A Barton</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Abundant Life Fellowship – Evanston</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2190 Wasatch Rd</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Evanston</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>82930</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>307-789-5868</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>stillcreektimf@gmail.com</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Tim Floyd</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Cody Assembly of God</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1532 Bleistein Ave</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Cody</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>82414</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>307-527-7339</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>codyassembly@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Cheri Cortez</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Destiny Church</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>711 Warren</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Cheyenne</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>82003</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>307-634-4657</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>destinychurchrick@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Rick McGraw</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Douglas Assembly of God</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>501 S 4th St</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>82633</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>307-358-3619</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>brossignol85@gmail.com</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Brian Rossignol</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Gillette</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>601 Carey</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Gillette</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>82716</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>307-682-3308</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>dmholden@juno.com</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Dan Holden</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Riverton</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>701 E Adams</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Riverton</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>82501</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>307-856-3637</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>mmbrumback@gmail.com</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Michael Brumback</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Rock Springs</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2191 Century Blvd</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Rock Springs</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>82902</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>307-362-8665</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>tnheidt@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Nicole Heidt</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Sheridan</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1045 Lewis St</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Sheridan</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>82801</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>307-674-6372</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>firstassemblysheridan@gmail.com</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Glad Tidings Assembly of God</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>777 E 7th St</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Powell</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>82435</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>307-754-2333</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>pastormikewalsh@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Michael Walsh</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Green River Assembly of God</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1380 Hitching Post Dr</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Green River</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>82935</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>307-875-6232</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>agfirstgr@gmail.com</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Shawn Johnston</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Impact Ministries</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>956 Maple St</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Wheatland</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>82201</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>307-331-7544</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>jharoldson.impact@hotmail.com</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>impactwy.org</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Jeremy Haroldson</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Living Waters Assembly of God</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>318 N 8th St</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Thermopolis</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>82443</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>307-864-3677</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>lwagthermopolis@gmail.com</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Michael Muench</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>New Life Assembly of God – Buffalo</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>6 Barstad Way</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>82834</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>307-684-5755</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Josh &amp; Whitney Davies</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>New Life Assembly of God – Laramie</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>3905 E Grey Cable</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Laramie</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>82072</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>307-460-3351</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>info@newlifelaramie.org</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Matt Baumgartner</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Radius Church</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>4301 Casper Mountain Rd</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Casper</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>82601</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>307-265-9121</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>contact@radiuschurch.life</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Craig Mellendorf</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Summit Church – Big Piney</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>3 Winkelman Ave</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Marbleton</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>83113</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>307-875-5212</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>summitchurchwy@gmail.com</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sunrise Assembly of God – Sheridan</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>570 Marion St</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Sheridan</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>82801</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>307-674-8424</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>nnjjjackson@gmail.com</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>John Jackson</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Trinity Assembly of God</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>604 9th St</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Rawlins</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>82301</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>307-324-2635</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>kk_sherman@hotmail.com</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Kirk Sherman</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>Wilderness Church</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>110 N Jackson St</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>Pinedale</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>WY</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E284" t="inlineStr">
         <is>
           <t>82941</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>307-749-8478</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G284" t="inlineStr">
         <is>
           <t>wcwyoming@gmail.com</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H284" t="inlineStr">
         <is>
           <t>wildernesschurchpinedale.com</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I284" t="inlineStr">
         <is>
           <t>Duke Edwards</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Bridger Valley Assembly of God</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2507 Hwy 414</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>82939</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>307-786-2303</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>bvag307@gmail.com</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>First Assembly of God – Sheridan WY</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1045 Lewis St</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Sheridan</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>82801</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>307-674-6372</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>firstassemblysheridan@gmail.com</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Hullett Assembly of God</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>252 Hunter</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Hulett</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>82720</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>307-467-5757</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>pastorclbauman@hotmail.com</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Charles Bauman</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Journey – Torrington</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1701 E F St</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Torrington</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>82240</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>307-575-7701</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>kingowingit@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Dale Harper</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Lighthouse Assembly of God – Pine Bluffs</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Fifth and Market</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Pine Bluffs</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>82082</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>307-245-3822</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>smanzanares13@gmail.com</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Steve Manzanares</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Lighthouse Assembly of God – Upton</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1320 Church St</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Upton</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>82730</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>307-468-2501</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Lighthouse Worship Center – Glenrock</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>201 N 3rd St</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Glenrock</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>82637</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>307-359-1228</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>tlschowengerdt@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Ted Schowengerdt</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Lovell Assembly of God</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>310 Idaho</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Lovell</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>82431</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>307-548-7105</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>lovellassembly@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Daniel Jarvis</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Miracle Valley Assembly of God</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>5601 HR Ranch Rd</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Cheyenne</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>82007</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>307-433-9999</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>miraclevalleyministries.org</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Mount Calvary Fellowship</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>200 N 3rd</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Worland</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>82401</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>307-347-4454</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>mtcalvaryagwy@gmail.com</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Mountain View Assembly – Ten Sleep</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>243 Second and Willow</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Ten Sleep</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>82442</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>307-366-2525</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>pastorbrandonweddle@gmail.com</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>New Hope Fellowship – Etna</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>32 Country Rd 108</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Etna</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>83118</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>307-883-6050</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>bizon1960@gmail.com</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Mark Halford</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>New Life Christian Center – Worland</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1028 Rd 11</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Worland</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>82401</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>307-347-2310</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>nlcc@trconnect.net</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>newlifeworland.com</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Larry Ramsfield</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Newcastle Assembly of God</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>216 S Seneca Ave</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>82701</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>307-746-2249</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>naogc@rtconnect.net</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Norman Brotzman</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Platte Valley Christian Center</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>111 N 7th St</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Saratoga</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>82331</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>307-326-5520</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>gmsmith1959@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Eugene Smith</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Prairie View Assembly of God</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>514 Bison</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>82732</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>307-464-1182</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>rjones_750@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Ricky Jones</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Restoration Fellowship International</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>522 Capital</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Cheyenne</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>82007</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>307-635-3184</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>rficheyenne.org</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>The Orchards Church</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>183 Main St</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Lander</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>82520</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>toddapettibone@gmail.com</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Todd &amp; Angela Pettibone</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Valley Worship Center – Hood River WY</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>5780 Highway 35</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>307-352-7269</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>valleyworshipcenter.pastor@gmail.com</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>valleyworshipcenter.org</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Way of the Cross</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>635 S 2nd St W</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Riverton</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>82501</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>307-851-5139</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>wotcag@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Wheatland Worship Center</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1452 Cedar St</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Wheatland</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>82201</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>307-322-2508</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>goni4@juno.com</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Geoffrey Gonifas</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
         <is>
           <t>WY</t>
         </is>
